--- a/public/exports/29189846.xlsx
+++ b/public/exports/29189846.xlsx
@@ -81,16 +81,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100010159</t>
+          <t xml:space="preserve">100163924</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F2">
-        <v>1178</v>
+        <v>294</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -281,16 +281,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1508276, 100535682</t>
+          <t xml:space="preserve">3448648</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F6">
-        <v>854</v>
+        <v>1399</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -336,11 +336,11 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F7">
-        <v>1399</v>
+        <v>2428</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -386,11 +386,11 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F8">
-        <v>2428</v>
+        <v>308</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -436,11 +436,11 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F9">
-        <v>308</v>
+        <v>1260</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -486,11 +486,11 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F10">
-        <v>1260</v>
+        <v>2501</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -531,16 +531,16 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3448648</t>
+          <t xml:space="preserve">3459673</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F11">
-        <v>2501</v>
+        <v>2756</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">3459673</t>
+          <t xml:space="preserve">378877, 378878</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="F12">
-        <v>2756</v>
+        <v>594</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -631,16 +631,16 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">379367, 379368</t>
+          <t xml:space="preserve">379367</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F13">
-        <v>3295</v>
+        <v>1906</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -681,16 +681,16 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">4001083</t>
+          <t xml:space="preserve">379367, 379368</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F14">
-        <v>1783</v>
+        <v>3295</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -731,16 +731,16 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">4001083, 100767459</t>
+          <t xml:space="preserve">379840, 379841</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F15">
-        <v>1522</v>
+        <v>3301</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -781,16 +781,16 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">4001990</t>
+          <t xml:space="preserve">379841</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F16">
-        <v>1281</v>
+        <v>280</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -831,12 +831,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">4002616</t>
+          <t xml:space="preserve">379841</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F17">
@@ -881,16 +881,16 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">4019941</t>
+          <t xml:space="preserve">381021, 381022, 381023, 381024, 381025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F18">
-        <v>397</v>
+        <v>1814</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">4027660</t>
+          <t xml:space="preserve">383714, 383715, 383716</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F19">
-        <v>616</v>
+        <v>6680</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">4047266</t>
+          <t xml:space="preserve">384187, 384188</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="F20">
-        <v>429</v>
+        <v>3245</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5584920</t>
+          <t xml:space="preserve">385146</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="F21">
-        <v>324</v>
+        <v>729</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1081,16 +1081,16 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5584939</t>
+          <t xml:space="preserve">385146</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F22">
-        <v>3383</v>
+        <v>1405</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1131,16 +1131,16 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5585905</t>
+          <t xml:space="preserve">4001083</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F23">
-        <v>418</v>
+        <v>1783</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1181,16 +1181,16 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">5591308</t>
+          <t xml:space="preserve">4001083, 100767459</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F24">
-        <v>634</v>
+        <v>1522</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1231,16 +1231,16 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5592392</t>
+          <t xml:space="preserve">4001990</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F25">
-        <v>838</v>
+        <v>1281</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1281,16 +1281,16 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5594838</t>
+          <t xml:space="preserve">4002616</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F26">
-        <v>308</v>
+        <v>280</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1331,16 +1331,16 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">5594838</t>
+          <t xml:space="preserve">4019941</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F27">
-        <v>2288</v>
+        <v>397</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">5594838</t>
+          <t xml:space="preserve">4027660</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F28">
-        <v>2252</v>
+        <v>616</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1431,16 +1431,16 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">748921, 3449805</t>
+          <t xml:space="preserve">4047266</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F29">
-        <v>2093</v>
+        <v>429</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">748922, 4012552</t>
+          <t xml:space="preserve">5584920</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="F30">
-        <v>259</v>
+        <v>324</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">748930, 5589566</t>
+          <t xml:space="preserve">5584939</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="F31">
-        <v>554</v>
+        <v>3383</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">748946, 3450059</t>
+          <t xml:space="preserve">5591308</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="F32">
-        <v>254</v>
+        <v>634</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1631,16 +1631,16 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">748947, 7651466</t>
+          <t xml:space="preserve">5592392</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F33">
-        <v>394</v>
+        <v>838</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1681,16 +1681,16 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">748948, 3452362</t>
+          <t xml:space="preserve">5594838</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F34">
-        <v>3087</v>
+        <v>308</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1731,16 +1731,16 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">748948, 3452362</t>
+          <t xml:space="preserve">5594838</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F35">
-        <v>1089</v>
+        <v>2288</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1781,16 +1781,16 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">748948, 3452362</t>
+          <t xml:space="preserve">5594838</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F36">
-        <v>380</v>
+        <v>2252</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1831,16 +1831,16 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">748952, 3448659</t>
+          <t xml:space="preserve">748921, 3449805</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F37">
-        <v>564</v>
+        <v>2093</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">748953, 5591283</t>
+          <t xml:space="preserve">748922, 4012552</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1890,7 +1890,7 @@
         </is>
       </c>
       <c r="F38">
-        <v>786</v>
+        <v>259</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1931,16 +1931,16 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">748953, 5591283</t>
+          <t xml:space="preserve">748930, 5589566</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F39">
-        <v>652</v>
+        <v>554</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1981,16 +1981,16 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">748953, 5591283</t>
+          <t xml:space="preserve">748946, 3450059</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F40">
-        <v>2232</v>
+        <v>254</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2031,16 +2031,16 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">748954, 5585905</t>
+          <t xml:space="preserve">748947, 7651466</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F41">
-        <v>1652</v>
+        <v>394</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">748967, 3451467</t>
+          <t xml:space="preserve">748952, 3448659</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="F42">
-        <v>4999</v>
+        <v>564</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2131,16 +2131,16 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">748986, 4019941</t>
+          <t xml:space="preserve">748953, 5591283</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F43">
-        <v>310</v>
+        <v>786</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2181,16 +2181,16 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">748988, 7536592</t>
+          <t xml:space="preserve">748953, 5591283</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F44">
-        <v>391</v>
+        <v>652</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2231,16 +2231,16 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">748988, 7536592</t>
+          <t xml:space="preserve">748953, 5591283</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F45">
-        <v>793</v>
+        <v>2232</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">749019, 4002026</t>
+          <t xml:space="preserve">748967, 3451467</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2290,7 +2290,7 @@
         </is>
       </c>
       <c r="F46">
-        <v>1188</v>
+        <v>4999</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2331,16 +2331,16 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">749021, 4009009</t>
+          <t xml:space="preserve">748986, 4019941</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F47">
-        <v>269</v>
+        <v>310</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2381,16 +2381,16 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">749028, 4001549</t>
+          <t xml:space="preserve">748988, 7536592</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F48">
-        <v>316</v>
+        <v>391</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2431,16 +2431,16 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">749029, 4001663</t>
+          <t xml:space="preserve">748988, 7536592</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F49">
-        <v>315</v>
+        <v>793</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2481,16 +2481,16 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">749065, 3460266</t>
+          <t xml:space="preserve">749019, 4002026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F50">
-        <v>278</v>
+        <v>1188</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2531,16 +2531,16 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">749074, 3459673</t>
+          <t xml:space="preserve">749021, 4009009</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F51">
-        <v>424</v>
+        <v>269</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2581,16 +2581,16 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">749074, 3459673</t>
+          <t xml:space="preserve">749028, 4001549</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F52">
-        <v>433</v>
+        <v>316</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2631,16 +2631,16 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">749074, 3459673</t>
+          <t xml:space="preserve">749029, 4001663</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F53">
-        <v>1587</v>
+        <v>315</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2681,16 +2681,16 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">749086, 3455213</t>
+          <t xml:space="preserve">749065, 3460266</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F54">
-        <v>1580</v>
+        <v>278</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2731,16 +2731,16 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">749101, 9299740</t>
+          <t xml:space="preserve">749074, 3459673</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F55">
-        <v>655</v>
+        <v>424</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2781,16 +2781,16 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">749126, 5585905</t>
+          <t xml:space="preserve">749074, 3459673</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F56">
-        <v>297</v>
+        <v>433</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">7580188</t>
+          <t xml:space="preserve">749074, 3459673</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F57">
-        <v>879</v>
+        <v>1587</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">7651466</t>
+          <t xml:space="preserve">749086, 3455213</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="F58">
-        <v>285</v>
+        <v>1580</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2931,16 +2931,16 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">7651466</t>
+          <t xml:space="preserve">749101, 9299740</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F59">
-        <v>340</v>
+        <v>655</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2981,16 +2981,16 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">8159310</t>
+          <t xml:space="preserve">7580188</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F60">
-        <v>342</v>
+        <v>879</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3031,16 +3031,16 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">9021620</t>
+          <t xml:space="preserve">7651466</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F61">
-        <v>1153</v>
+        <v>285</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3081,16 +3081,16 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">9214926</t>
+          <t xml:space="preserve">7651466</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F62">
-        <v>375</v>
+        <v>340</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">9387240</t>
+          <t xml:space="preserve">9021620</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3140,7 +3140,7 @@
         </is>
       </c>
       <c r="F63">
-        <v>5776</v>
+        <v>1153</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3231,30 +3231,30 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">9676964</t>
+          <t xml:space="preserve">748948, 3452362</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F65">
-        <v>974</v>
+        <v>3087</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200012931</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-04-28</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3281,25 +3281,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">3464210</t>
+          <t xml:space="preserve">748948, 3452362</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="F66">
-        <v>359</v>
+        <v>1089</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">200019807</t>
+          <t xml:space="preserve">200012931</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-01</t>
+          <t xml:space="preserve">2019-04-28</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3331,25 +3331,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1508163</t>
+          <t xml:space="preserve">748948, 3452362</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="F67">
-        <v>744</v>
+        <v>380</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">200019972</t>
+          <t xml:space="preserve">200012931</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-04</t>
+          <t xml:space="preserve">2019-04-28</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">3452362</t>
+          <t xml:space="preserve">3464210</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3390,16 +3390,16 @@
         </is>
       </c>
       <c r="F68">
-        <v>6940</v>
+        <v>359</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020044</t>
+          <t xml:space="preserve">200019807</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-07</t>
+          <t xml:space="preserve">2019-09-01</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">7860089</t>
+          <t xml:space="preserve">1508163</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3440,16 +3440,16 @@
         </is>
       </c>
       <c r="F69">
-        <v>2470</v>
+        <v>744</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020395</t>
+          <t xml:space="preserve">200019972</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-14</t>
+          <t xml:space="preserve">2019-09-04</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">7536592</t>
+          <t xml:space="preserve">3452362</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3490,16 +3490,16 @@
         </is>
       </c>
       <c r="F70">
-        <v>428</v>
+        <v>6940</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">200021397</t>
+          <t xml:space="preserve">200020044</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-30</t>
+          <t xml:space="preserve">2019-09-07</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3531,25 +3531,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">5590293</t>
+          <t xml:space="preserve">7860089</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F71">
-        <v>1272</v>
+        <v>2470</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057308</t>
+          <t xml:space="preserve">200020395</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-02-09</t>
+          <t xml:space="preserve">2019-09-14</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3581,25 +3581,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">5590305</t>
+          <t xml:space="preserve">9676964</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F72">
-        <v>1820</v>
+        <v>974</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057338</t>
+          <t xml:space="preserve">100135239</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-02-10</t>
+          <t xml:space="preserve">2019-09-24</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">8408062</t>
+          <t xml:space="preserve">7536592</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3640,16 +3640,16 @@
         </is>
       </c>
       <c r="F73">
-        <v>19217</v>
+        <v>428</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">200058375</t>
+          <t xml:space="preserve">200021397</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-03-23</t>
+          <t xml:space="preserve">2019-09-30</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">5590305</t>
+          <t xml:space="preserve">100010159</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3690,16 +3690,16 @@
         </is>
       </c>
       <c r="F74">
-        <v>1998</v>
+        <v>1178</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311039749</t>
+          <t xml:space="preserve">200049938</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-02-25</t>
+          <t xml:space="preserve">2021-06-07</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3731,25 +3731,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">10018933</t>
+          <t xml:space="preserve">5590293</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F75">
-        <v>1512</v>
+        <v>1272</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311110838</t>
+          <t xml:space="preserve">200057308</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-05</t>
+          <t xml:space="preserve">2022-02-09</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3781,25 +3781,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">3464052</t>
+          <t xml:space="preserve">5590305</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F76">
-        <v>731</v>
+        <v>1820</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311112072</t>
+          <t xml:space="preserve">200057338</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-11</t>
+          <t xml:space="preserve">2022-02-10</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3831,25 +3831,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">5587390</t>
+          <t xml:space="preserve">8408062</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">40</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F77">
-        <v>3175</v>
+        <v>19217</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311117732</t>
+          <t xml:space="preserve">200058375</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-06-08</t>
+          <t xml:space="preserve">2022-03-23</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3881,25 +3881,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">4003338</t>
+          <t xml:space="preserve">9387240</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F78">
-        <v>941</v>
+        <v>5776</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311165746</t>
+          <t xml:space="preserve">310038124</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-18</t>
+          <t xml:space="preserve">2023-05-03</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3931,25 +3931,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">5590174</t>
+          <t xml:space="preserve">8159310</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F79">
-        <v>1716</v>
+        <v>342</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311196137</t>
+          <t xml:space="preserve">311035322</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-23</t>
+          <t xml:space="preserve">2024-01-24</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">5594838</t>
+          <t xml:space="preserve">5590305</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3990,26 +3990,26 @@
         </is>
       </c>
       <c r="F80">
-        <v>7565</v>
+        <v>1998</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219394</t>
+          <t xml:space="preserve">311039749</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-22</t>
+          <t xml:space="preserve">2024-02-25</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">8316127</t>
+          <t xml:space="preserve">10018933</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4040,26 +4040,26 @@
         </is>
       </c>
       <c r="F81">
-        <v>684</v>
+        <v>1512</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311233296</t>
+          <t xml:space="preserve">311110838</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-10</t>
+          <t xml:space="preserve">2025-05-05</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -4081,35 +4081,35 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">8316127</t>
+          <t xml:space="preserve">5587390</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">40</t>
         </is>
       </c>
       <c r="F82">
-        <v>1306</v>
+        <v>3175</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311233299</t>
+          <t xml:space="preserve">311117732</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-10</t>
+          <t xml:space="preserve">2025-06-08</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">8316127</t>
+          <t xml:space="preserve">4003338</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4140,26 +4140,26 @@
         </is>
       </c>
       <c r="F83">
-        <v>3127</v>
+        <v>941</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311233299</t>
+          <t xml:space="preserve">311165746</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-10</t>
+          <t xml:space="preserve">2026-03-18</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -4181,35 +4181,35 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">10163918</t>
+          <t xml:space="preserve">5590174</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F84">
-        <v>439</v>
+        <v>1716</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374808</t>
+          <t xml:space="preserve">311196137</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-05</t>
+          <t xml:space="preserve">2026-08-23</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">4011534</t>
+          <t xml:space="preserve">5594838</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4240,16 +4240,16 @@
         </is>
       </c>
       <c r="F85">
-        <v>3558</v>
+        <v>7565</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372378</t>
+          <t xml:space="preserve">311219394</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-05</t>
+          <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4281,25 +4281,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">4011534</t>
+          <t xml:space="preserve">8316127</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F86">
-        <v>1305</v>
+        <v>684</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372345</t>
+          <t xml:space="preserve">311233296</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-05</t>
+          <t xml:space="preserve">2027-03-10</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4331,25 +4331,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">4011534</t>
+          <t xml:space="preserve">8316127</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F87">
-        <v>1450</v>
+        <v>1306</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372344</t>
+          <t xml:space="preserve">311233299</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-05</t>
+          <t xml:space="preserve">2027-03-10</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4381,25 +4381,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">5585079</t>
+          <t xml:space="preserve">8316127</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F88">
-        <v>2507</v>
+        <v>3127</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372546</t>
+          <t xml:space="preserve">311233299</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-05</t>
+          <t xml:space="preserve">2027-03-10</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">5589767</t>
+          <t xml:space="preserve">10163918</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4440,11 +4440,11 @@
         </is>
       </c>
       <c r="F89">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373775</t>
+          <t xml:space="preserve">311374808</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">5594584</t>
+          <t xml:space="preserve">4011534</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4490,11 +4490,11 @@
         </is>
       </c>
       <c r="F90">
-        <v>904</v>
+        <v>3558</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373112</t>
+          <t xml:space="preserve">311372346</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4531,20 +4531,20 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">7434905</t>
+          <t xml:space="preserve">4011534</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F91">
-        <v>306</v>
+        <v>1305</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369551</t>
+          <t xml:space="preserve">311372345</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4581,20 +4581,20 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">7434905</t>
+          <t xml:space="preserve">4011534</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F92">
-        <v>275</v>
+        <v>1450</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369547</t>
+          <t xml:space="preserve">311372344</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4631,20 +4631,20 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">9470397</t>
+          <t xml:space="preserve">5585079</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F93">
-        <v>1133</v>
+        <v>2507</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311277020</t>
+          <t xml:space="preserve">311372546</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4681,25 +4681,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">5589413</t>
+          <t xml:space="preserve">5589767</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F94">
-        <v>746</v>
+        <v>443</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311368625</t>
+          <t xml:space="preserve">311373775</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-10</t>
+          <t xml:space="preserve">2027-10-05</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">7597884</t>
+          <t xml:space="preserve">5594584</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4740,16 +4740,16 @@
         </is>
       </c>
       <c r="F95">
-        <v>395</v>
+        <v>904</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311377726</t>
+          <t xml:space="preserve">311373112</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-10</t>
+          <t xml:space="preserve">2027-10-05</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4781,25 +4781,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">10007506</t>
+          <t xml:space="preserve">7434905</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F96">
-        <v>271</v>
+        <v>306</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373094</t>
+          <t xml:space="preserve">311369544</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-23</t>
+          <t xml:space="preserve">2027-10-05</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4831,25 +4831,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">10007506</t>
+          <t xml:space="preserve">7434905</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F97">
-        <v>518</v>
+        <v>275</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279890</t>
+          <t xml:space="preserve">311369544</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-23</t>
+          <t xml:space="preserve">2027-10-05</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4881,25 +4881,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">10007506</t>
+          <t xml:space="preserve">9470397</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F98">
-        <v>419</v>
+        <v>1133</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279891</t>
+          <t xml:space="preserve">311277020</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-23</t>
+          <t xml:space="preserve">2027-10-05</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">10044154</t>
+          <t xml:space="preserve">7597884</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4940,16 +4940,16 @@
         </is>
       </c>
       <c r="F99">
-        <v>376</v>
+        <v>395</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311385266</t>
+          <t xml:space="preserve">311377726</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-23</t>
+          <t xml:space="preserve">2027-10-10</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4981,20 +4981,20 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">10044154</t>
+          <t xml:space="preserve">10007506</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F100">
-        <v>376</v>
+        <v>271</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311385269</t>
+          <t xml:space="preserve">311373094</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -5031,20 +5031,20 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">10044154</t>
+          <t xml:space="preserve">10007506</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F101">
-        <v>380</v>
+        <v>518</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375079</t>
+          <t xml:space="preserve">311279890</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -5081,20 +5081,20 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">10044154</t>
+          <t xml:space="preserve">10007506</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F102">
-        <v>380</v>
+        <v>419</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311385260</t>
+          <t xml:space="preserve">311279891</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">3450589</t>
+          <t xml:space="preserve">10044154</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -5140,11 +5140,11 @@
         </is>
       </c>
       <c r="F103">
-        <v>1530</v>
+        <v>376</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375607</t>
+          <t xml:space="preserve">311385266</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -5181,20 +5181,20 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">5587281</t>
+          <t xml:space="preserve">10044154</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F104">
-        <v>672</v>
+        <v>376</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375058</t>
+          <t xml:space="preserve">311385269</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -5231,20 +5231,20 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">5588297</t>
+          <t xml:space="preserve">10044154</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F105">
-        <v>464</v>
+        <v>380</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374763</t>
+          <t xml:space="preserve">311375079</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -5281,20 +5281,20 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">5592392</t>
+          <t xml:space="preserve">10044154</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F106">
-        <v>911</v>
+        <v>380</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375973</t>
+          <t xml:space="preserve">311385260</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">8762612</t>
+          <t xml:space="preserve">3450589</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -5340,11 +5340,11 @@
         </is>
       </c>
       <c r="F107">
-        <v>359</v>
+        <v>1530</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311368615</t>
+          <t xml:space="preserve">311375607</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">8838224</t>
+          <t xml:space="preserve">5587281</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -5390,11 +5390,11 @@
         </is>
       </c>
       <c r="F108">
-        <v>690</v>
+        <v>672</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374131</t>
+          <t xml:space="preserve">311375058</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">9249170</t>
+          <t xml:space="preserve">5588297</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -5440,11 +5440,11 @@
         </is>
       </c>
       <c r="F109">
-        <v>252</v>
+        <v>464</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311368635</t>
+          <t xml:space="preserve">311374763</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">9768065</t>
+          <t xml:space="preserve">5592392</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -5490,11 +5490,11 @@
         </is>
       </c>
       <c r="F110">
-        <v>843</v>
+        <v>911</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373858</t>
+          <t xml:space="preserve">311375973</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">3454452</t>
+          <t xml:space="preserve">8762612</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -5540,16 +5540,16 @@
         </is>
       </c>
       <c r="F111">
-        <v>5129</v>
+        <v>359</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375954</t>
+          <t xml:space="preserve">311368615</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-08</t>
+          <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5581,25 +5581,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">3454452</t>
+          <t xml:space="preserve">8838224</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F112">
-        <v>580</v>
+        <v>690</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373802</t>
+          <t xml:space="preserve">311374131</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-08</t>
+          <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">3461997</t>
+          <t xml:space="preserve">9249170</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -5640,16 +5640,16 @@
         </is>
       </c>
       <c r="F113">
-        <v>643</v>
+        <v>252</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372955</t>
+          <t xml:space="preserve">311368635</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-08</t>
+          <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5681,25 +5681,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">379841</t>
+          <t xml:space="preserve">9768065</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F114">
-        <v>280</v>
+        <v>843</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311282692</t>
+          <t xml:space="preserve">311373858</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-08</t>
+          <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5731,20 +5731,20 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">379841</t>
+          <t xml:space="preserve">3454452</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F115">
-        <v>280</v>
+        <v>5129</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311282692</t>
+          <t xml:space="preserve">311375954</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -5781,20 +5781,20 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">4001591</t>
+          <t xml:space="preserve">3454452</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F116">
-        <v>768</v>
+        <v>580</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311376497</t>
+          <t xml:space="preserve">311373802</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">4002652</t>
+          <t xml:space="preserve">3461997</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -5840,11 +5840,11 @@
         </is>
       </c>
       <c r="F117">
-        <v>599</v>
+        <v>643</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372391</t>
+          <t xml:space="preserve">311282769</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">4005866</t>
+          <t xml:space="preserve">4001591</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -5890,11 +5890,11 @@
         </is>
       </c>
       <c r="F118">
-        <v>405</v>
+        <v>768</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369171</t>
+          <t xml:space="preserve">311282687</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5931,20 +5931,20 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">4027745</t>
+          <t xml:space="preserve">4002652</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F119">
-        <v>374</v>
+        <v>599</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372960</t>
+          <t xml:space="preserve">311372391</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5981,20 +5981,20 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">5585098</t>
+          <t xml:space="preserve">4005866</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F120">
-        <v>498</v>
+        <v>405</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311282841</t>
+          <t xml:space="preserve">311369171</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -6036,15 +6036,15 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="F121">
-        <v>334</v>
+        <v>498</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375039</t>
+          <t xml:space="preserve">311282841</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -6081,20 +6081,20 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">5587271</t>
+          <t xml:space="preserve">5585098</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="F122">
-        <v>3762</v>
+        <v>334</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369791</t>
+          <t xml:space="preserve">311375039</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">5588250</t>
+          <t xml:space="preserve">5587271</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -6140,11 +6140,11 @@
         </is>
       </c>
       <c r="F123">
-        <v>8068</v>
+        <v>3762</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372348</t>
+          <t xml:space="preserve">311369791</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -6181,20 +6181,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">5589413</t>
+          <t xml:space="preserve">5588250</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F124">
-        <v>257</v>
+        <v>8068</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311368618</t>
+          <t xml:space="preserve">311282669</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373116</t>
+          <t xml:space="preserve">311282785</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373117</t>
+          <t xml:space="preserve">311282785</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372417</t>
+          <t xml:space="preserve">311372416</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311368943</t>
+          <t xml:space="preserve">311284535</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372407</t>
+          <t xml:space="preserve">311284519</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372407</t>
+          <t xml:space="preserve">311284519</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372407</t>
+          <t xml:space="preserve">311284519</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372407</t>
+          <t xml:space="preserve">311284519</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -7481,20 +7481,20 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">5589413</t>
+          <t xml:space="preserve">8094912</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F150">
-        <v>1646</v>
+        <v>254</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311368623</t>
+          <t xml:space="preserve">311372408</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -7531,20 +7531,20 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">5589413</t>
+          <t xml:space="preserve">8438883</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F151">
-        <v>296</v>
+        <v>4263</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374067</t>
+          <t xml:space="preserve">311372337</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">8094912</t>
+          <t xml:space="preserve">8548393</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -7590,11 +7590,11 @@
         </is>
       </c>
       <c r="F152">
-        <v>254</v>
+        <v>404</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372408</t>
+          <t xml:space="preserve">311374050</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">8438883</t>
+          <t xml:space="preserve">9228374</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -7640,11 +7640,11 @@
         </is>
       </c>
       <c r="F153">
-        <v>4263</v>
+        <v>1287</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372337</t>
+          <t xml:space="preserve">311374800</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">8548393</t>
+          <t xml:space="preserve">1440274</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -7690,16 +7690,16 @@
         </is>
       </c>
       <c r="F154">
-        <v>404</v>
+        <v>1992</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374050</t>
+          <t xml:space="preserve">311285411</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-19</t>
+          <t xml:space="preserve">2027-11-23</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -7731,25 +7731,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">9228374</t>
+          <t xml:space="preserve">1440274</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F155">
-        <v>1287</v>
+        <v>392</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374800</t>
+          <t xml:space="preserve">311285411</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-19</t>
+          <t xml:space="preserve">2027-11-23</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -7786,15 +7786,15 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F156">
-        <v>1992</v>
+        <v>1508</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369175</t>
+          <t xml:space="preserve">311285411</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -7831,20 +7831,20 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">1440274</t>
+          <t xml:space="preserve">4028052</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F157">
-        <v>392</v>
+        <v>637</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369175</t>
+          <t xml:space="preserve">311374098</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -7881,20 +7881,20 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">1440274</t>
+          <t xml:space="preserve">4029105</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F158">
-        <v>1508</v>
+        <v>402</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369175</t>
+          <t xml:space="preserve">311285375</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -7931,20 +7931,20 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">4028052</t>
+          <t xml:space="preserve">4048067</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F159">
-        <v>637</v>
+        <v>327</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374098</t>
+          <t xml:space="preserve">311369238</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -7981,20 +7981,20 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">4029105</t>
+          <t xml:space="preserve">8159310</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F160">
-        <v>402</v>
+        <v>627</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285375</t>
+          <t xml:space="preserve">311369765</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -8031,20 +8031,20 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">4048067</t>
+          <t xml:space="preserve">8272317</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F161">
-        <v>327</v>
+        <v>506</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369238</t>
+          <t xml:space="preserve">311372926</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -8081,20 +8081,20 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">8159310</t>
+          <t xml:space="preserve">9907696</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F162">
-        <v>627</v>
+        <v>540</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369765</t>
+          <t xml:space="preserve">311285395</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">8272317</t>
+          <t xml:space="preserve">9989609</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -8140,11 +8140,11 @@
         </is>
       </c>
       <c r="F163">
-        <v>506</v>
+        <v>568</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372926</t>
+          <t xml:space="preserve">311373095</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -8181,25 +8181,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">9907696</t>
+          <t xml:space="preserve">10163918</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F164">
-        <v>540</v>
+        <v>933</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285395</t>
+          <t xml:space="preserve">311287081</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-23</t>
+          <t xml:space="preserve">2027-12-04</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">9989609</t>
+          <t xml:space="preserve">3448158</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -8240,16 +8240,16 @@
         </is>
       </c>
       <c r="F165">
-        <v>568</v>
+        <v>675</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373095</t>
+          <t xml:space="preserve">311373108</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-23</t>
+          <t xml:space="preserve">2027-12-04</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -8281,20 +8281,20 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">10163918</t>
+          <t xml:space="preserve">4001592</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F166">
-        <v>933</v>
+        <v>460</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287081</t>
+          <t xml:space="preserve">311287056</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -8331,20 +8331,20 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">3448158</t>
+          <t xml:space="preserve">4001592</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F167">
-        <v>675</v>
+        <v>498</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373108</t>
+          <t xml:space="preserve">311287056</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">4001592</t>
+          <t xml:space="preserve">4020459</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -8390,11 +8390,11 @@
         </is>
       </c>
       <c r="F168">
-        <v>460</v>
+        <v>320</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372945</t>
+          <t xml:space="preserve">311372655</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -8431,20 +8431,20 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">4001592</t>
+          <t xml:space="preserve">5585905</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F169">
-        <v>498</v>
+        <v>9989</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287056</t>
+          <t xml:space="preserve">311287077</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -8481,20 +8481,20 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">4020459</t>
+          <t xml:space="preserve">5585905</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F170">
-        <v>320</v>
+        <v>418</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372655</t>
+          <t xml:space="preserve">311287077</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -8531,20 +8531,20 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">5585905</t>
+          <t xml:space="preserve">748954, 5585905</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F171">
-        <v>9989</v>
+        <v>1652</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375036</t>
+          <t xml:space="preserve">311287077</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -8581,25 +8581,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">3460688</t>
+          <t xml:space="preserve">749126, 5585905</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F172">
-        <v>395</v>
+        <v>297</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311376506</t>
+          <t xml:space="preserve">311287077</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-05</t>
+          <t xml:space="preserve">2027-12-04</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -8631,20 +8631,20 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">5589413</t>
+          <t xml:space="preserve">3460688</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F173">
-        <v>1017</v>
+        <v>395</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374080</t>
+          <t xml:space="preserve">311376506</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -8681,20 +8681,20 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">5589413</t>
+          <t xml:space="preserve">5591308</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F174">
-        <v>657</v>
+        <v>627</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311368609</t>
+          <t xml:space="preserve">311372539</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -8731,20 +8731,20 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">5589413</t>
+          <t xml:space="preserve">5591310</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F175">
-        <v>855</v>
+        <v>627</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311368821</t>
+          <t xml:space="preserve">311372537</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -8781,25 +8781,25 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">5589413</t>
+          <t xml:space="preserve">4001514</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F176">
-        <v>1180</v>
+        <v>8250</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374073</t>
+          <t xml:space="preserve">311375571</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-05</t>
+          <t xml:space="preserve">2027-12-15</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -8831,25 +8831,25 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">5591308</t>
+          <t xml:space="preserve">4001514</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F177">
-        <v>627</v>
+        <v>667</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372539</t>
+          <t xml:space="preserve">311375571</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-05</t>
+          <t xml:space="preserve">2027-12-15</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -8881,25 +8881,25 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">5591310</t>
+          <t xml:space="preserve">4001514</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F178">
-        <v>627</v>
+        <v>1142</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372537</t>
+          <t xml:space="preserve">311375571</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-05</t>
+          <t xml:space="preserve">2027-12-15</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -8936,11 +8936,11 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F179">
-        <v>8250</v>
+        <v>1887</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
@@ -8981,25 +8981,25 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">4001514</t>
+          <t xml:space="preserve">3468476</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F180">
-        <v>667</v>
+        <v>445</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375571</t>
+          <t xml:space="preserve">311375948</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-15</t>
+          <t xml:space="preserve">2027-12-16</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -9031,25 +9031,25 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">4001514</t>
+          <t xml:space="preserve">10044156</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F181">
-        <v>1142</v>
+        <v>1146</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375571</t>
+          <t xml:space="preserve">311375061</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-15</t>
+          <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -9081,25 +9081,25 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">4001514</t>
+          <t xml:space="preserve">10050852</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F182">
-        <v>1887</v>
+        <v>640</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375571</t>
+          <t xml:space="preserve">311289212</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-15</t>
+          <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -9131,25 +9131,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">3468476</t>
+          <t xml:space="preserve">3452362</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F183">
-        <v>445</v>
+        <v>1685</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375948</t>
+          <t xml:space="preserve">311377727</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-16</t>
+          <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">10044156</t>
+          <t xml:space="preserve">4028294</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -9190,11 +9190,11 @@
         </is>
       </c>
       <c r="F184">
-        <v>1146</v>
+        <v>817</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375061</t>
+          <t xml:space="preserve">311374101</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -9231,20 +9231,20 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">10050852</t>
+          <t xml:space="preserve">4048007</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F185">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372982</t>
+          <t xml:space="preserve">311372423</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -9281,20 +9281,20 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">3452362</t>
+          <t xml:space="preserve">5585133</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F186">
-        <v>1685</v>
+        <v>2155</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311377727</t>
+          <t xml:space="preserve">311373088</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -9331,20 +9331,20 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">4028294</t>
+          <t xml:space="preserve">5586340</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F187">
-        <v>817</v>
+        <v>289</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374101</t>
+          <t xml:space="preserve">311289296</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -9381,20 +9381,20 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">4048007</t>
+          <t xml:space="preserve">5586340</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F188">
-        <v>632</v>
+        <v>1391</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372423</t>
+          <t xml:space="preserve">311289296</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -9431,20 +9431,20 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">5585133</t>
+          <t xml:space="preserve">5587704</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F189">
-        <v>2155</v>
+        <v>808</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373089</t>
+          <t xml:space="preserve">311369518</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -9481,20 +9481,20 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">5586340</t>
+          <t xml:space="preserve">5589433</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F190">
-        <v>289</v>
+        <v>1018</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289301</t>
+          <t xml:space="preserve">311375635</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -9531,20 +9531,20 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">5586340</t>
+          <t xml:space="preserve">5590156</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F191">
-        <v>1391</v>
+        <v>861</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372406</t>
+          <t xml:space="preserve">311374132</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -9581,20 +9581,20 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">5587704</t>
+          <t xml:space="preserve">5592049</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F192">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369534</t>
+          <t xml:space="preserve">311368686</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">5589433</t>
+          <t xml:space="preserve">5592843</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -9640,11 +9640,11 @@
         </is>
       </c>
       <c r="F193">
-        <v>1018</v>
+        <v>697</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375635</t>
+          <t xml:space="preserve">311373829</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -9681,7 +9681,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t xml:space="preserve">5590156</t>
+          <t xml:space="preserve">7085015</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -9690,11 +9690,11 @@
         </is>
       </c>
       <c r="F194">
-        <v>861</v>
+        <v>1009</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374132</t>
+          <t xml:space="preserve">311375959</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -9731,7 +9731,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t xml:space="preserve">5592049</t>
+          <t xml:space="preserve">7916686</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -9740,11 +9740,11 @@
         </is>
       </c>
       <c r="F195">
-        <v>833</v>
+        <v>258</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311368686</t>
+          <t xml:space="preserve">311289245</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -9781,20 +9781,20 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t xml:space="preserve">5592843</t>
+          <t xml:space="preserve">7916686</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F196">
-        <v>697</v>
+        <v>651</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373829</t>
+          <t xml:space="preserve">311369795</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -9831,20 +9831,20 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t xml:space="preserve">7085015</t>
+          <t xml:space="preserve">7916686</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F197">
-        <v>1009</v>
+        <v>489</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375959</t>
+          <t xml:space="preserve">311289247</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -9886,15 +9886,15 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F198">
-        <v>258</v>
+        <v>298</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289245</t>
+          <t xml:space="preserve">311289248</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -9936,15 +9936,15 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F199">
-        <v>651</v>
+        <v>4345</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369840</t>
+          <t xml:space="preserve">311369795</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -9986,15 +9986,15 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F200">
-        <v>489</v>
+        <v>3045</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289247</t>
+          <t xml:space="preserve">311369795</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -10036,15 +10036,15 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F201">
-        <v>298</v>
+        <v>2856</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289248</t>
+          <t xml:space="preserve">311369795</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -10086,15 +10086,15 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F202">
-        <v>4345</v>
+        <v>3456</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369822</t>
+          <t xml:space="preserve">311369795</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -10136,15 +10136,15 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F203">
-        <v>3045</v>
+        <v>419</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375953</t>
+          <t xml:space="preserve">311289254</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -10181,20 +10181,20 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t xml:space="preserve">7916686</t>
+          <t xml:space="preserve">7954632</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F204">
-        <v>2856</v>
+        <v>745</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369828</t>
+          <t xml:space="preserve">311372398</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -10231,20 +10231,20 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t xml:space="preserve">7916686</t>
+          <t xml:space="preserve">8070299</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F205">
-        <v>3456</v>
+        <v>787</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369834</t>
+          <t xml:space="preserve">311372415</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -10281,20 +10281,20 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t xml:space="preserve">7916686</t>
+          <t xml:space="preserve">8070299</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F206">
-        <v>419</v>
+        <v>565</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289254</t>
+          <t xml:space="preserve">311372412</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -10331,7 +10331,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t xml:space="preserve">7954632</t>
+          <t xml:space="preserve">8344237</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -10340,11 +10340,11 @@
         </is>
       </c>
       <c r="F207">
-        <v>745</v>
+        <v>1460</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372398</t>
+          <t xml:space="preserve">311375544</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -10381,20 +10381,20 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t xml:space="preserve">8070299</t>
+          <t xml:space="preserve">8344237</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F208">
-        <v>787</v>
+        <v>419</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372415</t>
+          <t xml:space="preserve">311289325</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -10431,20 +10431,20 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t xml:space="preserve">8070299</t>
+          <t xml:space="preserve">8344237</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F209">
-        <v>565</v>
+        <v>3750</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372412</t>
+          <t xml:space="preserve">311375547</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t xml:space="preserve">8344237</t>
+          <t xml:space="preserve">8586170</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -10490,11 +10490,11 @@
         </is>
       </c>
       <c r="F210">
-        <v>1460</v>
+        <v>465</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375544</t>
+          <t xml:space="preserve">311375967</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -10531,20 +10531,20 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t xml:space="preserve">8344237</t>
+          <t xml:space="preserve">8604830</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F211">
-        <v>419</v>
+        <v>483</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289325</t>
+          <t xml:space="preserve">311373105</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -10581,20 +10581,20 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t xml:space="preserve">8344237</t>
+          <t xml:space="preserve">8975801</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F212">
-        <v>3750</v>
+        <v>700</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375547</t>
+          <t xml:space="preserve">311375583</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -10631,20 +10631,20 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t xml:space="preserve">8371196</t>
+          <t xml:space="preserve">9215002</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t xml:space="preserve">61</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F213">
-        <v>923</v>
+        <v>395</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289337</t>
+          <t xml:space="preserve">311375537</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t xml:space="preserve">8586170</t>
+          <t xml:space="preserve">3458397</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -10690,16 +10690,16 @@
         </is>
       </c>
       <c r="F214">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375967</t>
+          <t xml:space="preserve">311368882</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-18</t>
+          <t xml:space="preserve">2027-12-19</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -10731,25 +10731,25 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t xml:space="preserve">8604830</t>
+          <t xml:space="preserve">3458397</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F215">
-        <v>483</v>
+        <v>1040</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373105</t>
+          <t xml:space="preserve">311368888</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-18</t>
+          <t xml:space="preserve">2027-12-19</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -10781,25 +10781,25 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t xml:space="preserve">8975801</t>
+          <t xml:space="preserve">3458397</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F216">
-        <v>700</v>
+        <v>445</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375583</t>
+          <t xml:space="preserve">311368892</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-18</t>
+          <t xml:space="preserve">2027-12-19</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -10831,25 +10831,25 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t xml:space="preserve">9215002</t>
+          <t xml:space="preserve">3459673</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F217">
-        <v>395</v>
+        <v>540</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375537</t>
+          <t xml:space="preserve">311369763</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-18</t>
+          <t xml:space="preserve">2027-12-19</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t xml:space="preserve">3458397</t>
+          <t xml:space="preserve">4002616</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -10890,11 +10890,11 @@
         </is>
       </c>
       <c r="F218">
-        <v>473</v>
+        <v>530</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311368882</t>
+          <t xml:space="preserve">311372335</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -10931,20 +10931,20 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t xml:space="preserve">3458397</t>
+          <t xml:space="preserve">7421720</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F219">
-        <v>1040</v>
+        <v>568</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311368888</t>
+          <t xml:space="preserve">311372970</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -10981,20 +10981,20 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t xml:space="preserve">3458397</t>
+          <t xml:space="preserve">7775696</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F220">
-        <v>445</v>
+        <v>373</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311368892</t>
+          <t xml:space="preserve">311373133</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -11031,20 +11031,20 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t xml:space="preserve">3459673</t>
+          <t xml:space="preserve">7775696</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F221">
-        <v>540</v>
+        <v>1233</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369763</t>
+          <t xml:space="preserve">311369497</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -11081,7 +11081,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t xml:space="preserve">4002616</t>
+          <t xml:space="preserve">8509351</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -11090,11 +11090,11 @@
         </is>
       </c>
       <c r="F222">
-        <v>530</v>
+        <v>2671</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372335</t>
+          <t xml:space="preserve">311369807</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -11131,7 +11131,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t xml:space="preserve">7421720</t>
+          <t xml:space="preserve">9305221</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -11140,11 +11140,11 @@
         </is>
       </c>
       <c r="F223">
-        <v>568</v>
+        <v>544</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372970</t>
+          <t xml:space="preserve">311372334</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -11181,7 +11181,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t xml:space="preserve">7775696</t>
+          <t xml:space="preserve">9702318</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -11190,11 +11190,11 @@
         </is>
       </c>
       <c r="F224">
-        <v>373</v>
+        <v>326</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373133</t>
+          <t xml:space="preserve">311368643</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -11231,7 +11231,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t xml:space="preserve">7775696</t>
+          <t xml:space="preserve">9702318</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -11240,11 +11240,11 @@
         </is>
       </c>
       <c r="F225">
-        <v>1233</v>
+        <v>292</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369497</t>
+          <t xml:space="preserve">311372966</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -11281,7 +11281,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t xml:space="preserve">8509351</t>
+          <t xml:space="preserve">100009033</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -11290,16 +11290,16 @@
         </is>
       </c>
       <c r="F226">
-        <v>2671</v>
+        <v>449</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369807</t>
+          <t xml:space="preserve">311373765</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-19</t>
+          <t xml:space="preserve">2027-12-22</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -11331,7 +11331,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t xml:space="preserve">9305221</t>
+          <t xml:space="preserve">4019920</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -11340,16 +11340,16 @@
         </is>
       </c>
       <c r="F227">
-        <v>544</v>
+        <v>554</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372334</t>
+          <t xml:space="preserve">311290270</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-19</t>
+          <t xml:space="preserve">2027-12-22</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t xml:space="preserve">9702318</t>
+          <t xml:space="preserve">4019935</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -11390,16 +11390,16 @@
         </is>
       </c>
       <c r="F228">
-        <v>326</v>
+        <v>665</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311368643</t>
+          <t xml:space="preserve">311374083</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-19</t>
+          <t xml:space="preserve">2027-12-22</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -11431,25 +11431,25 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t xml:space="preserve">9702318</t>
+          <t xml:space="preserve">4027707</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F229">
-        <v>292</v>
+        <v>2457</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372966</t>
+          <t xml:space="preserve">311290232</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-19</t>
+          <t xml:space="preserve">2027-12-22</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -11481,20 +11481,20 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t xml:space="preserve">100009033</t>
+          <t xml:space="preserve">4027745</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F230">
-        <v>449</v>
+        <v>374</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373765</t>
+          <t xml:space="preserve">311372426</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -11531,7 +11531,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t xml:space="preserve">378877, 378878</t>
+          <t xml:space="preserve">4028026</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -11540,11 +11540,11 @@
         </is>
       </c>
       <c r="F231">
-        <v>594</v>
+        <v>475</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374046</t>
+          <t xml:space="preserve">311373788</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -11581,20 +11581,20 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t xml:space="preserve">4019920</t>
+          <t xml:space="preserve">4047266</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F232">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374093</t>
+          <t xml:space="preserve">311372599</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -11631,7 +11631,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t xml:space="preserve">4019935</t>
+          <t xml:space="preserve">9699622</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -11640,11 +11640,11 @@
         </is>
       </c>
       <c r="F233">
-        <v>665</v>
+        <v>918</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374083</t>
+          <t xml:space="preserve">311290239</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -11681,20 +11681,20 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t xml:space="preserve">4027707</t>
+          <t xml:space="preserve">9907696</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F234">
-        <v>2457</v>
+        <v>597</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290232</t>
+          <t xml:space="preserve">311372420</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -11731,20 +11731,20 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t xml:space="preserve">4028026</t>
+          <t xml:space="preserve">9907696</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F235">
-        <v>475</v>
+        <v>656</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373788</t>
+          <t xml:space="preserve">311372421</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -11781,25 +11781,25 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t xml:space="preserve">4047266</t>
+          <t xml:space="preserve">5584682</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F236">
-        <v>551</v>
+        <v>756</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372599</t>
+          <t xml:space="preserve">311375956</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-22</t>
+          <t xml:space="preserve">2027-12-23</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -11831,25 +11831,25 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t xml:space="preserve">8371196</t>
+          <t xml:space="preserve">5584682</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F237">
-        <v>388</v>
+        <v>925</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290198</t>
+          <t xml:space="preserve">311375956</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-22</t>
+          <t xml:space="preserve">2027-12-23</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -11881,25 +11881,25 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t xml:space="preserve">8371196</t>
+          <t xml:space="preserve">5584682</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F238">
-        <v>388</v>
+        <v>7694</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290199</t>
+          <t xml:space="preserve">311375956</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-22</t>
+          <t xml:space="preserve">2027-12-23</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -11931,25 +11931,25 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t xml:space="preserve">8371196</t>
+          <t xml:space="preserve">5584682</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t xml:space="preserve">60</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F239">
-        <v>269</v>
+        <v>327</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311368688</t>
+          <t xml:space="preserve">311375956</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-22</t>
+          <t xml:space="preserve">2027-12-23</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -11981,7 +11981,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t xml:space="preserve">9254134</t>
+          <t xml:space="preserve">10050851</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -11990,16 +11990,16 @@
         </is>
       </c>
       <c r="F240">
-        <v>288</v>
+        <v>3511</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290281</t>
+          <t xml:space="preserve">311372340</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-22</t>
+          <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -12031,25 +12031,25 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t xml:space="preserve">9699622</t>
+          <t xml:space="preserve">10050851</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F241">
-        <v>918</v>
+        <v>2154</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290239</t>
+          <t xml:space="preserve">311372340</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-22</t>
+          <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -12081,7 +12081,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t xml:space="preserve">9907696</t>
+          <t xml:space="preserve">10050851</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -12090,16 +12090,16 @@
         </is>
       </c>
       <c r="F242">
-        <v>597</v>
+        <v>970</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372420</t>
+          <t xml:space="preserve">311372340</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-22</t>
+          <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -12131,7 +12131,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t xml:space="preserve">9907696</t>
+          <t xml:space="preserve">10050851</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -12140,16 +12140,16 @@
         </is>
       </c>
       <c r="F243">
-        <v>656</v>
+        <v>2234</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372421</t>
+          <t xml:space="preserve">311372340</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-22</t>
+          <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -12181,25 +12181,25 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t xml:space="preserve">5584682</t>
+          <t xml:space="preserve">10050851</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F244">
-        <v>756</v>
+        <v>2345</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375956</t>
+          <t xml:space="preserve">311372340</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-23</t>
+          <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -12231,25 +12231,25 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t xml:space="preserve">5584682</t>
+          <t xml:space="preserve">10050851</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F245">
-        <v>925</v>
+        <v>835</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375956</t>
+          <t xml:space="preserve">311372340</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-23</t>
+          <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -12281,25 +12281,25 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t xml:space="preserve">5584682</t>
+          <t xml:space="preserve">3448162</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F246">
-        <v>7694</v>
+        <v>3610</v>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375956</t>
+          <t xml:space="preserve">311372553</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-23</t>
+          <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -12331,25 +12331,25 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t xml:space="preserve">5584682</t>
+          <t xml:space="preserve">3448162</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F247">
-        <v>327</v>
+        <v>1716</v>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375956</t>
+          <t xml:space="preserve">311372593</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-23</t>
+          <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -12381,20 +12381,20 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t xml:space="preserve">100163924</t>
+          <t xml:space="preserve">3448162</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F248">
-        <v>294</v>
+        <v>370</v>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373819</t>
+          <t xml:space="preserve">311372568</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -12431,20 +12431,20 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t xml:space="preserve">10050851</t>
+          <t xml:space="preserve">3448162</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F249">
-        <v>3511</v>
+        <v>922</v>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372340</t>
+          <t xml:space="preserve">311372578</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -12481,20 +12481,20 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t xml:space="preserve">10050851</t>
+          <t xml:space="preserve">3448162</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F250">
-        <v>2154</v>
+        <v>1649</v>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372340</t>
+          <t xml:space="preserve">311372586</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -12531,20 +12531,20 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t xml:space="preserve">10050851</t>
+          <t xml:space="preserve">3448162</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F251">
-        <v>970</v>
+        <v>1591</v>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372340</t>
+          <t xml:space="preserve">311372592</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -12581,20 +12581,20 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t xml:space="preserve">10050851</t>
+          <t xml:space="preserve">3448348</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F252">
-        <v>2234</v>
+        <v>642</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372340</t>
+          <t xml:space="preserve">311368645</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -12631,20 +12631,20 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t xml:space="preserve">10050851</t>
+          <t xml:space="preserve">3449342</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F253">
-        <v>2345</v>
+        <v>3922</v>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372340</t>
+          <t xml:space="preserve">311375968</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -12681,20 +12681,20 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t xml:space="preserve">10050851</t>
+          <t xml:space="preserve">3449342</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F254">
-        <v>835</v>
+        <v>1173</v>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372340</t>
+          <t xml:space="preserve">311368679</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -12731,20 +12731,20 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t xml:space="preserve">3448162</t>
+          <t xml:space="preserve">3449342</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F255">
-        <v>3610</v>
+        <v>1629</v>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372553</t>
+          <t xml:space="preserve">311290590</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -12781,20 +12781,20 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t xml:space="preserve">3448162</t>
+          <t xml:space="preserve">3453194</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F256">
-        <v>1716</v>
+        <v>2405</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372593</t>
+          <t xml:space="preserve">311290512</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -12831,7 +12831,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t xml:space="preserve">3448162</t>
+          <t xml:space="preserve">3453194</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -12840,11 +12840,11 @@
         </is>
       </c>
       <c r="F257">
-        <v>370</v>
+        <v>1982</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372568</t>
+          <t xml:space="preserve">311372973</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -12881,20 +12881,20 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t xml:space="preserve">3448162</t>
+          <t xml:space="preserve">3460177</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F258">
-        <v>922</v>
+        <v>1178</v>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372578</t>
+          <t xml:space="preserve">311373799</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -12931,20 +12931,20 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t xml:space="preserve">3448162</t>
+          <t xml:space="preserve">3462726</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F259">
-        <v>1649</v>
+        <v>1471</v>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372586</t>
+          <t xml:space="preserve">311385384</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -12981,20 +12981,20 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t xml:space="preserve">3448162</t>
+          <t xml:space="preserve">3462726</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F260">
-        <v>1591</v>
+        <v>1796</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372592</t>
+          <t xml:space="preserve">311373080</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -13031,20 +13031,20 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t xml:space="preserve">3448348</t>
+          <t xml:space="preserve">3462726</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F261">
-        <v>642</v>
+        <v>314</v>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t xml:space="preserve">311368645</t>
+          <t xml:space="preserve">311373081</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -13081,20 +13081,20 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t xml:space="preserve">3449342</t>
+          <t xml:space="preserve">3462726</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F262">
-        <v>3922</v>
+        <v>355</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375968</t>
+          <t xml:space="preserve">311290518</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -13131,20 +13131,20 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t xml:space="preserve">3449342</t>
+          <t xml:space="preserve">3462726</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F263">
-        <v>1173</v>
+        <v>1538</v>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t xml:space="preserve">311368679</t>
+          <t xml:space="preserve">311373082</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -13181,20 +13181,20 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t xml:space="preserve">3449342</t>
+          <t xml:space="preserve">3462758</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F264">
-        <v>1629</v>
+        <v>720</v>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290590</t>
+          <t xml:space="preserve">311290563</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t xml:space="preserve">3453194</t>
+          <t xml:space="preserve">4000718</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -13240,11 +13240,11 @@
         </is>
       </c>
       <c r="F265">
-        <v>2405</v>
+        <v>3813</v>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t xml:space="preserve">311368944</t>
+          <t xml:space="preserve">311290529</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -13281,20 +13281,20 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t xml:space="preserve">3453194</t>
+          <t xml:space="preserve">4009260</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F266">
-        <v>1982</v>
+        <v>259</v>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372973</t>
+          <t xml:space="preserve">311369819</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -13331,7 +13331,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t xml:space="preserve">3460177</t>
+          <t xml:space="preserve">4009651</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -13340,11 +13340,11 @@
         </is>
       </c>
       <c r="F267">
-        <v>1178</v>
+        <v>366</v>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373799</t>
+          <t xml:space="preserve">311372551</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -13381,20 +13381,20 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t xml:space="preserve">3462726</t>
+          <t xml:space="preserve">5584909</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F268">
-        <v>1471</v>
+        <v>616</v>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t xml:space="preserve">311385384</t>
+          <t xml:space="preserve">311374110</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -13431,20 +13431,20 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t xml:space="preserve">3462726</t>
+          <t xml:space="preserve">5589413</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F269">
-        <v>1796</v>
+        <v>2365</v>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373080</t>
+          <t xml:space="preserve">311369509</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -13481,20 +13481,20 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t xml:space="preserve">3462726</t>
+          <t xml:space="preserve">5589413</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F270">
-        <v>314</v>
+        <v>1646</v>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373081</t>
+          <t xml:space="preserve">311374076</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -13531,20 +13531,20 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t xml:space="preserve">3462726</t>
+          <t xml:space="preserve">5589413</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F271">
-        <v>355</v>
+        <v>1017</v>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290518</t>
+          <t xml:space="preserve">311374076</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -13581,20 +13581,20 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t xml:space="preserve">3462726</t>
+          <t xml:space="preserve">5589413</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F272">
-        <v>1538</v>
+        <v>296</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373082</t>
+          <t xml:space="preserve">311374076</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -13631,20 +13631,20 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t xml:space="preserve">3462758</t>
+          <t xml:space="preserve">5589413</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="F273">
-        <v>720</v>
+        <v>257</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290563</t>
+          <t xml:space="preserve">311374076</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -13681,20 +13681,20 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t xml:space="preserve">379367</t>
+          <t xml:space="preserve">5589413</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F274">
-        <v>1906</v>
+        <v>657</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374054</t>
+          <t xml:space="preserve">311374076</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -13731,20 +13731,20 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t xml:space="preserve">383714, 383715, 383716</t>
+          <t xml:space="preserve">5589413</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="F275">
-        <v>6680</v>
+        <v>855</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375955</t>
+          <t xml:space="preserve">311374076</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -13781,20 +13781,20 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t xml:space="preserve">385146</t>
+          <t xml:space="preserve">5589413</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">36</t>
         </is>
       </c>
       <c r="F276">
-        <v>729</v>
+        <v>746</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374113</t>
+          <t xml:space="preserve">311374076</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -13831,20 +13831,20 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t xml:space="preserve">385146</t>
+          <t xml:space="preserve">5589413</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F277">
-        <v>1405</v>
+        <v>1180</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374125</t>
+          <t xml:space="preserve">311374076</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -13881,7 +13881,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000718</t>
+          <t xml:space="preserve">5590613</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -13890,11 +13890,11 @@
         </is>
       </c>
       <c r="F278">
-        <v>3813</v>
+        <v>11799</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369190</t>
+          <t xml:space="preserve">311290524</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -13931,7 +13931,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t xml:space="preserve">4009260</t>
+          <t xml:space="preserve">5591355</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -13940,11 +13940,11 @@
         </is>
       </c>
       <c r="F279">
-        <v>259</v>
+        <v>1342</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369819</t>
+          <t xml:space="preserve">311373835</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -13981,20 +13981,20 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t xml:space="preserve">4009651</t>
+          <t xml:space="preserve">5591355</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F280">
-        <v>366</v>
+        <v>1521</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372551</t>
+          <t xml:space="preserve">311373855</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -14031,20 +14031,20 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t xml:space="preserve">5584909</t>
+          <t xml:space="preserve">5591355</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F281">
-        <v>616</v>
+        <v>412</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374110</t>
+          <t xml:space="preserve">311373832</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -14081,7 +14081,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t xml:space="preserve">5589413</t>
+          <t xml:space="preserve">5593087</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -14090,11 +14090,11 @@
         </is>
       </c>
       <c r="F282">
-        <v>2365</v>
+        <v>578</v>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369509</t>
+          <t xml:space="preserve">311290570</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -14131,7 +14131,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t xml:space="preserve">5590613</t>
+          <t xml:space="preserve">8134651</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -14140,11 +14140,11 @@
         </is>
       </c>
       <c r="F283">
-        <v>11799</v>
+        <v>285</v>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373101</t>
+          <t xml:space="preserve">311373763</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -14181,7 +14181,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t xml:space="preserve">5591355</t>
+          <t xml:space="preserve">3454867</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -14190,16 +14190,16 @@
         </is>
       </c>
       <c r="F284">
-        <v>1342</v>
+        <v>273</v>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373835</t>
+          <t xml:space="preserve">311368613</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-27</t>
+          <t xml:space="preserve">2027-12-28</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -14231,25 +14231,25 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t xml:space="preserve">5591355</t>
+          <t xml:space="preserve">3454867</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F285">
-        <v>1521</v>
+        <v>488</v>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373855</t>
+          <t xml:space="preserve">311375099</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-27</t>
+          <t xml:space="preserve">2027-12-28</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -14281,7 +14281,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t xml:space="preserve">5591355</t>
+          <t xml:space="preserve">3454867</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -14290,16 +14290,16 @@
         </is>
       </c>
       <c r="F286">
-        <v>412</v>
+        <v>284</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373832</t>
+          <t xml:space="preserve">311375099</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-27</t>
+          <t xml:space="preserve">2027-12-28</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -14331,7 +14331,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t xml:space="preserve">5593087</t>
+          <t xml:space="preserve">3468562</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -14340,16 +14340,16 @@
         </is>
       </c>
       <c r="F287">
-        <v>578</v>
+        <v>5165</v>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290570</t>
+          <t xml:space="preserve">311375628</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-27</t>
+          <t xml:space="preserve">2027-12-28</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -14381,25 +14381,25 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t xml:space="preserve">8134651</t>
+          <t xml:space="preserve">3468562</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F288">
-        <v>285</v>
+        <v>813</v>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373763</t>
+          <t xml:space="preserve">311290695</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-27</t>
+          <t xml:space="preserve">2027-12-28</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -14431,7 +14431,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t xml:space="preserve">3454867</t>
+          <t xml:space="preserve">4001548</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -14440,11 +14440,11 @@
         </is>
       </c>
       <c r="F289">
-        <v>273</v>
+        <v>662</v>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t xml:space="preserve">311368613</t>
+          <t xml:space="preserve">311374764</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -14481,20 +14481,20 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t xml:space="preserve">3454867</t>
+          <t xml:space="preserve">4002019</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F290">
-        <v>488</v>
+        <v>7205</v>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375102</t>
+          <t xml:space="preserve">311290661</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -14531,20 +14531,20 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t xml:space="preserve">3454867</t>
+          <t xml:space="preserve">4012634</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F291">
-        <v>284</v>
+        <v>387</v>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375108</t>
+          <t xml:space="preserve">311375598</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -14581,20 +14581,20 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t xml:space="preserve">3468562</t>
+          <t xml:space="preserve">5589413</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="F292">
-        <v>5165</v>
+        <v>1281</v>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375628</t>
+          <t xml:space="preserve">311375539</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -14631,20 +14631,20 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t xml:space="preserve">3468562</t>
+          <t xml:space="preserve">5591355</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F293">
-        <v>813</v>
+        <v>3916</v>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290695</t>
+          <t xml:space="preserve">311375512</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -14681,20 +14681,20 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t xml:space="preserve">4001548</t>
+          <t xml:space="preserve">7095022</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F294">
-        <v>662</v>
+        <v>1521</v>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374764</t>
+          <t xml:space="preserve">311376499</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -14731,20 +14731,20 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t xml:space="preserve">4002019</t>
+          <t xml:space="preserve">7095022</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F295">
-        <v>7205</v>
+        <v>4683</v>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374769</t>
+          <t xml:space="preserve">311376499</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -14781,7 +14781,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t xml:space="preserve">4012634</t>
+          <t xml:space="preserve">8074164</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -14790,11 +14790,11 @@
         </is>
       </c>
       <c r="F296">
-        <v>387</v>
+        <v>722</v>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375598</t>
+          <t xml:space="preserve">311375648</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -14831,20 +14831,20 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t xml:space="preserve">5589413</t>
+          <t xml:space="preserve">8223290</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F297">
-        <v>1281</v>
+        <v>930</v>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375539</t>
+          <t xml:space="preserve">311290666</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -14881,20 +14881,20 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t xml:space="preserve">5591355</t>
+          <t xml:space="preserve">8838279</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F298">
-        <v>3916</v>
+        <v>284</v>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375512</t>
+          <t xml:space="preserve">311290692</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -14931,20 +14931,20 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t xml:space="preserve">7095022</t>
+          <t xml:space="preserve">9214993</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F299">
-        <v>1521</v>
+        <v>3989</v>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t xml:space="preserve">311376499</t>
+          <t xml:space="preserve">311375640</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -14981,20 +14981,20 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t xml:space="preserve">7095022</t>
+          <t xml:space="preserve">9214993</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F300">
-        <v>4683</v>
+        <v>2310</v>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t xml:space="preserve">311376499</t>
+          <t xml:space="preserve">311375640</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -15031,7 +15031,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t xml:space="preserve">8074164</t>
+          <t xml:space="preserve">9431029</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -15040,11 +15040,11 @@
         </is>
       </c>
       <c r="F301">
-        <v>722</v>
+        <v>1500</v>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375648</t>
+          <t xml:space="preserve">311368829</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t xml:space="preserve">8223290</t>
+          <t xml:space="preserve">9214926</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -15090,16 +15090,16 @@
         </is>
       </c>
       <c r="F302">
-        <v>930</v>
+        <v>2661</v>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374773</t>
+          <t xml:space="preserve">311372662</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-28</t>
+          <t xml:space="preserve">2027-12-29</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -15131,25 +15131,25 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t xml:space="preserve">8838279</t>
+          <t xml:space="preserve">9214926</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F303">
-        <v>284</v>
+        <v>1945</v>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290692</t>
+          <t xml:space="preserve">311372662</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-28</t>
+          <t xml:space="preserve">2027-12-29</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -15181,25 +15181,25 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t xml:space="preserve">9214993</t>
+          <t xml:space="preserve">9214926</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F304">
-        <v>3989</v>
+        <v>375</v>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375640</t>
+          <t xml:space="preserve">311372662</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-28</t>
+          <t xml:space="preserve">2027-12-29</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -15231,25 +15231,25 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t xml:space="preserve">9214993</t>
+          <t xml:space="preserve">9214926</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F305">
-        <v>2310</v>
+        <v>422</v>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375640</t>
+          <t xml:space="preserve">311372662</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-28</t>
+          <t xml:space="preserve">2027-12-29</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -15281,25 +15281,25 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t xml:space="preserve">9431029</t>
+          <t xml:space="preserve">9214926</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F306">
-        <v>1500</v>
+        <v>1025</v>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t xml:space="preserve">311368829</t>
+          <t xml:space="preserve">311372662</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-28</t>
+          <t xml:space="preserve">2027-12-29</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -15336,15 +15336,15 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F307">
-        <v>2661</v>
+        <v>898</v>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372723</t>
+          <t xml:space="preserve">311372662</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -15381,25 +15381,25 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t xml:space="preserve">9214926</t>
+          <t xml:space="preserve">3451289</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F308">
-        <v>1945</v>
+        <v>1067</v>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372723</t>
+          <t xml:space="preserve">311290810</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-29</t>
+          <t xml:space="preserve">2027-12-30</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -15431,25 +15431,25 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t xml:space="preserve">9214926</t>
+          <t xml:space="preserve">3451289</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F309">
-        <v>422</v>
+        <v>444</v>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372723</t>
+          <t xml:space="preserve">311290810</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-29</t>
+          <t xml:space="preserve">2027-12-30</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -15481,25 +15481,25 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t xml:space="preserve">9214926</t>
+          <t xml:space="preserve">3451289</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="F310">
-        <v>1025</v>
+        <v>976</v>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372723</t>
+          <t xml:space="preserve">311290810</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-29</t>
+          <t xml:space="preserve">2027-12-30</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -15531,25 +15531,25 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t xml:space="preserve">9214926</t>
+          <t xml:space="preserve">3451289</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F311">
-        <v>898</v>
+        <v>1673</v>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372723</t>
+          <t xml:space="preserve">311290810</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-29</t>
+          <t xml:space="preserve">2027-12-30</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -15586,11 +15586,11 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F312">
-        <v>1067</v>
+        <v>3803</v>
       </c>
       <c r="G312" t="inlineStr">
         <is>
@@ -15636,11 +15636,11 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F313">
-        <v>444</v>
+        <v>380</v>
       </c>
       <c r="G313" t="inlineStr">
         <is>
@@ -15686,15 +15686,15 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F314">
-        <v>976</v>
+        <v>306</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290810</t>
+          <t xml:space="preserve">311290811</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -15731,25 +15731,25 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t xml:space="preserve">3451289</t>
+          <t xml:space="preserve">3455227</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F315">
-        <v>1673</v>
+        <v>2628</v>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290810</t>
+          <t xml:space="preserve">311291101</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-30</t>
+          <t xml:space="preserve">2028-01-04</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -15781,25 +15781,25 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t xml:space="preserve">3451289</t>
+          <t xml:space="preserve">5591308</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F316">
-        <v>3803</v>
+        <v>384</v>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290810</t>
+          <t xml:space="preserve">311372532</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-30</t>
+          <t xml:space="preserve">2028-01-04</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -15831,25 +15831,25 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t xml:space="preserve">3451289</t>
+          <t xml:space="preserve">7715426</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F317">
-        <v>380</v>
+        <v>635</v>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290810</t>
+          <t xml:space="preserve">311291095</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-30</t>
+          <t xml:space="preserve">2028-01-04</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -15881,25 +15881,25 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t xml:space="preserve">3451289</t>
+          <t xml:space="preserve">8371196</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F318">
-        <v>306</v>
+        <v>388</v>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290811</t>
+          <t xml:space="preserve">311291089</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-30</t>
+          <t xml:space="preserve">2028-01-04</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -15931,20 +15931,20 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t xml:space="preserve">3455227</t>
+          <t xml:space="preserve">8371196</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F319">
-        <v>2628</v>
+        <v>388</v>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375525</t>
+          <t xml:space="preserve">311291089</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -15981,20 +15981,20 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t xml:space="preserve">379840, 379841</t>
+          <t xml:space="preserve">8371196</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="F320">
-        <v>3301</v>
+        <v>275</v>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291149</t>
+          <t xml:space="preserve">311291089</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -16031,20 +16031,20 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t xml:space="preserve">5591308</t>
+          <t xml:space="preserve">8371196</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">60</t>
         </is>
       </c>
       <c r="F321">
-        <v>384</v>
+        <v>269</v>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372532</t>
+          <t xml:space="preserve">311291089</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -16081,20 +16081,20 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t xml:space="preserve">7715426</t>
+          <t xml:space="preserve">8371196</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">61</t>
         </is>
       </c>
       <c r="F322">
-        <v>635</v>
+        <v>923</v>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373742</t>
+          <t xml:space="preserve">311291089</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -16131,20 +16131,20 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t xml:space="preserve">8371196</t>
+          <t xml:space="preserve">9254134</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F323">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291090</t>
+          <t xml:space="preserve">311291092</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -16344,7 +16344,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373757</t>
+          <t xml:space="preserve">311293774</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -16444,7 +16444,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372613</t>
+          <t xml:space="preserve">311293836</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -16494,7 +16494,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374196</t>
+          <t xml:space="preserve">311293836</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -16536,15 +16536,15 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F331">
-        <v>2275</v>
+        <v>731</v>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293831</t>
+          <t xml:space="preserve">311293836</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -16586,15 +16586,15 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F332">
-        <v>297</v>
+        <v>2275</v>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374191</t>
+          <t xml:space="preserve">311293831</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -16636,15 +16636,15 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F333">
-        <v>333</v>
+        <v>297</v>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293833</t>
+          <t xml:space="preserve">311293836</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -16681,20 +16681,20 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t xml:space="preserve">5587531</t>
+          <t xml:space="preserve">3464052</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F334">
-        <v>836</v>
+        <v>333</v>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379580</t>
+          <t xml:space="preserve">311293833</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -16736,7 +16736,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F335">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379580</t>
+          <t xml:space="preserve">311293801</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -16781,20 +16781,20 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940099</t>
+          <t xml:space="preserve">5587531</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F336">
-        <v>1569</v>
+        <v>836</v>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374142</t>
+          <t xml:space="preserve">311293850</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -16831,25 +16831,25 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t xml:space="preserve">4011561</t>
+          <t xml:space="preserve">8940099</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F337">
-        <v>1178</v>
+        <v>1569</v>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369993</t>
+          <t xml:space="preserve">311374136</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-04-09</t>
+          <t xml:space="preserve">2028-01-22</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -16881,25 +16881,25 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t xml:space="preserve">3464853</t>
+          <t xml:space="preserve">1508276, 100535682</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F338">
-        <v>335</v>
+        <v>854</v>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t xml:space="preserve">311467972</t>
+          <t xml:space="preserve">311373759</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-19</t>
+          <t xml:space="preserve">2028-02-15</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -16931,25 +16931,25 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t xml:space="preserve">5586340</t>
+          <t xml:space="preserve">4011561</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F339">
-        <v>313</v>
+        <v>1178</v>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t xml:space="preserve">311476458</t>
+          <t xml:space="preserve">311369993</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-17</t>
+          <t xml:space="preserve">2029-04-09</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -16981,25 +16981,25 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t xml:space="preserve">100124844</t>
+          <t xml:space="preserve">3464853</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F340">
-        <v>1565</v>
+        <v>335</v>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t xml:space="preserve">311505527</t>
+          <t xml:space="preserve">311467972</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-22</t>
+          <t xml:space="preserve">2030-10-19</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -17031,25 +17031,25 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t xml:space="preserve">749066, 3456742</t>
+          <t xml:space="preserve">5586340</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F341">
-        <v>348</v>
+        <v>313</v>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540479</t>
+          <t xml:space="preserve">311476458</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-12</t>
+          <t xml:space="preserve">2030-11-17</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -17081,7 +17081,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t xml:space="preserve">384187, 384188</t>
+          <t xml:space="preserve">100124844</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -17090,16 +17090,16 @@
         </is>
       </c>
       <c r="F342">
-        <v>3245</v>
+        <v>1565</v>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t xml:space="preserve">311619862</t>
+          <t xml:space="preserve">311505527</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-11</t>
+          <t xml:space="preserve">2031-03-22</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -17131,25 +17131,25 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t xml:space="preserve">5589417</t>
+          <t xml:space="preserve">749066, 3456742</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F343">
-        <v>8141</v>
+        <v>348</v>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652390</t>
+          <t xml:space="preserve">311540479</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-04</t>
+          <t xml:space="preserve">2031-08-12</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -17181,25 +17181,25 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t xml:space="preserve">5590613</t>
+          <t xml:space="preserve">5589417</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F344">
-        <v>478</v>
+        <v>8141</v>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t xml:space="preserve">311659256</t>
+          <t xml:space="preserve">311652390</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-09</t>
+          <t xml:space="preserve">2033-01-04</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -17231,25 +17231,25 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t xml:space="preserve">5586340</t>
+          <t xml:space="preserve">5590613</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F345">
-        <v>357</v>
+        <v>478</v>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661783</t>
+          <t xml:space="preserve">311659256</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-22</t>
+          <t xml:space="preserve">2033-02-09</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -17281,25 +17281,25 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t xml:space="preserve">381021, 381022, 381023, 381024, 381025</t>
+          <t xml:space="preserve">5586340</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F346">
-        <v>1814</v>
+        <v>357</v>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t xml:space="preserve">311702960</t>
+          <t xml:space="preserve">311661783</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-27</t>
+          <t xml:space="preserve">2033-02-22</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">

--- a/public/exports/29189846.xlsx
+++ b/public/exports/29189846.xlsx
@@ -19734,7 +19734,7 @@
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374194</t>
+          <t xml:space="preserve">311293836</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">

--- a/public/exports/29189846.xlsx
+++ b/public/exports/29189846.xlsx
@@ -3414,7 +3414,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">200019807</t>
+          <t xml:space="preserve">200019808</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369551</t>
+          <t xml:space="preserve">311369544</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369547</t>
+          <t xml:space="preserve">311369544</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372407</t>
+          <t xml:space="preserve">311284519</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372407</t>
+          <t xml:space="preserve">311284519</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372407</t>
+          <t xml:space="preserve">311284519</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372407</t>
+          <t xml:space="preserve">311284519</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311368943</t>
+          <t xml:space="preserve">311284535</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -9294,7 +9294,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372945</t>
+          <t xml:space="preserve">311287056</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375036</t>
+          <t xml:space="preserve">311287077</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369840</t>
+          <t xml:space="preserve">311369795</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -10734,7 +10734,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369534</t>
+          <t xml:space="preserve">311369518</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369828</t>
+          <t xml:space="preserve">311369795</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289254</t>
+          <t xml:space="preserve">311369795</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -10974,7 +10974,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289247</t>
+          <t xml:space="preserve">311369795</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -11094,7 +11094,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369822</t>
+          <t xml:space="preserve">311369795</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -11154,7 +11154,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375953</t>
+          <t xml:space="preserve">311369795</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369834</t>
+          <t xml:space="preserve">311369795</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -11574,7 +11574,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289301</t>
+          <t xml:space="preserve">311289296</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372406</t>
+          <t xml:space="preserve">311289296</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -12234,7 +12234,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375635</t>
+          <t xml:space="preserve">311375639</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -13554,7 +13554,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374093</t>
+          <t xml:space="preserve">311290270</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -14454,7 +14454,7 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t xml:space="preserve">311368944</t>
+          <t xml:space="preserve">311290512</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369190</t>
+          <t xml:space="preserve">311290531</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -15054,7 +15054,7 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369509</t>
+          <t xml:space="preserve">311374076</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -17154,7 +17154,7 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374769</t>
+          <t xml:space="preserve">311290664</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372723</t>
+          <t xml:space="preserve">311372662</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
@@ -17994,7 +17994,7 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372723</t>
+          <t xml:space="preserve">311372662</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
@@ -18114,7 +18114,7 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372723</t>
+          <t xml:space="preserve">311372662</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
@@ -18174,7 +18174,7 @@
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372723</t>
+          <t xml:space="preserve">311372662</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
@@ -18234,7 +18234,7 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372723</t>
+          <t xml:space="preserve">311372662</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
@@ -18714,7 +18714,7 @@
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291090</t>
+          <t xml:space="preserve">311291089</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375525</t>
+          <t xml:space="preserve">311291101</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
@@ -19374,7 +19374,7 @@
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379580</t>
+          <t xml:space="preserve">311293801</t>
         </is>
       </c>
       <c r="J323" t="inlineStr">
@@ -19494,7 +19494,7 @@
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373757</t>
+          <t xml:space="preserve">311293774</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
@@ -19914,7 +19914,7 @@
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374196</t>
+          <t xml:space="preserve">311293836</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293833</t>
+          <t xml:space="preserve">311293836</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
@@ -20094,7 +20094,7 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374191</t>
+          <t xml:space="preserve">311293836</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">

--- a/public/exports/29189846.xlsx
+++ b/public/exports/29189846.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L352"/>
+  <dimension ref="A1:M352"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -724,10 +779,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -784,10 +844,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -844,10 +909,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -904,10 +974,15 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -964,10 +1039,15 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1024,10 +1104,15 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1084,10 +1169,15 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1144,10 +1234,15 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1204,10 +1299,15 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1264,10 +1364,15 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1324,10 +1429,15 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1384,10 +1494,15 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1444,10 +1559,15 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1504,10 +1624,15 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1564,10 +1689,15 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1624,10 +1754,15 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1684,10 +1819,15 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1744,10 +1884,15 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1804,10 +1949,15 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1864,10 +2014,15 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1924,10 +2079,15 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1984,10 +2144,15 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2044,10 +2209,15 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2104,10 +2274,15 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2164,10 +2339,15 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2224,10 +2404,15 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2284,10 +2469,15 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2344,10 +2534,15 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2404,10 +2599,15 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2464,10 +2664,15 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2524,10 +2729,15 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2584,10 +2794,15 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2644,10 +2859,15 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2704,10 +2924,15 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2764,10 +2989,15 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2824,10 +3054,15 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2884,10 +3119,15 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2944,10 +3184,15 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3004,10 +3249,15 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3064,10 +3314,15 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3124,10 +3379,15 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3184,10 +3444,15 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3239,15 +3504,20 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-04-28</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3299,15 +3569,20 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-04-28</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3359,15 +3634,20 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-04-28</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3419,15 +3699,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t xml:space="preserve">Just A/S</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-01</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3479,15 +3764,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-04</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3539,15 +3829,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Leif Hansen Engineering A/S</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-07</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3599,15 +3894,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t xml:space="preserve">Leif Hansen Engineering A/S</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-14</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3659,15 +3959,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Viborg</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-24</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3719,15 +4024,20 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t xml:space="preserve">Just A/S</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-30</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3779,15 +4089,20 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-06-07</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3839,15 +4154,20 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t xml:space="preserve">Grontmij A/S</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-02-09</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3899,15 +4219,20 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-02-10</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3959,15 +4284,20 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-03-23</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4019,15 +4349,20 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-05-03</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4079,15 +4414,20 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t xml:space="preserve">factum2 viborg</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-01-24</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4139,15 +4479,20 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-02-25</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4199,15 +4544,20 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t xml:space="preserve">factum2 struer</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-05-05</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4259,15 +4609,20 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-06-08</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4319,15 +4674,20 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t xml:space="preserve">Conergi</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-03-18</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4379,15 +4739,20 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-08-23</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4439,15 +4804,20 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4499,15 +4869,20 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-10</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4559,15 +4934,20 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-10</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4619,15 +4999,20 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-10</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4674,20 +5059,25 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372378</t>
+          <t xml:space="preserve">311372346</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-05</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4734,20 +5124,25 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372345</t>
+          <t xml:space="preserve">311372346</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-05</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4794,20 +5189,25 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372344</t>
+          <t xml:space="preserve">311372346</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-05</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4859,15 +5259,20 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-05</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4919,15 +5324,20 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-05</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4979,15 +5389,20 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-05</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5039,15 +5454,20 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-05</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5094,20 +5514,25 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373775</t>
+          <t xml:space="preserve">311373778</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-05</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5159,15 +5584,20 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-05</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5219,15 +5649,20 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-05</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5279,15 +5714,20 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-10</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5339,15 +5779,20 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5394,20 +5839,25 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279891</t>
+          <t xml:space="preserve">311279903</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5459,15 +5909,20 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5514,20 +5969,25 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279890</t>
+          <t xml:space="preserve">311279903</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5579,15 +6039,20 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5639,15 +6104,20 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5699,15 +6169,20 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5759,15 +6234,20 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5819,15 +6299,20 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5879,15 +6364,20 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5939,15 +6429,20 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5999,15 +6494,20 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6059,15 +6559,20 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6119,15 +6624,20 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6179,15 +6689,20 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6239,15 +6754,20 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-08</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6299,15 +6819,20 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-08</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6354,20 +6879,25 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311376497</t>
+          <t xml:space="preserve">311282687</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-08</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6414,20 +6944,25 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372417</t>
+          <t xml:space="preserve">311372416</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-08</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6474,20 +7009,25 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372955</t>
+          <t xml:space="preserve">311282769</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-08</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6539,15 +7079,20 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-08</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6599,15 +7144,20 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-08</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6654,20 +7204,25 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373116</t>
+          <t xml:space="preserve">311282785</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-08</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6714,20 +7269,25 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373117</t>
+          <t xml:space="preserve">311282785</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-08</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6779,15 +7339,20 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-08</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6839,15 +7404,20 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-08</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6899,15 +7469,20 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-08</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6959,15 +7534,20 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-08</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7019,15 +7599,20 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-08</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7079,15 +7664,20 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-08</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7139,15 +7729,20 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-19</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7199,15 +7794,20 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-19</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7259,15 +7859,20 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-19</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7319,15 +7924,20 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-19</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7379,15 +7989,20 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-19</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7439,15 +8054,20 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-19</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7494,20 +8114,25 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311284535</t>
+          <t xml:space="preserve">311368606</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-19</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7559,15 +8184,20 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-19</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7619,15 +8249,20 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-19</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7679,15 +8314,20 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-19</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7739,15 +8379,20 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-19</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7794,20 +8439,25 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373751</t>
+          <t xml:space="preserve">311373752</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-19</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7859,15 +8509,20 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-19</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7919,15 +8574,20 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-19</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7979,15 +8639,20 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-19</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8039,15 +8704,20 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-19</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8099,15 +8769,20 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-19</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8159,15 +8834,20 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-19</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8219,15 +8899,20 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-19</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8279,15 +8964,20 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-19</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8339,15 +9029,20 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-19</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8399,15 +9094,20 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-19</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8459,15 +9159,20 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-19</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8519,15 +9224,20 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-19</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8579,15 +9289,20 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-19</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8639,15 +9354,20 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-19</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8699,15 +9419,20 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-23</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8759,15 +9484,20 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-23</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8819,15 +9549,20 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-23</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8879,15 +9614,20 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-23</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8934,20 +9674,25 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369175</t>
+          <t xml:space="preserve">311285411</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-23</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8994,20 +9739,25 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369175</t>
+          <t xml:space="preserve">311285411</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-23</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9054,20 +9804,25 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369175</t>
+          <t xml:space="preserve">311285411</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-23</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9119,15 +9874,20 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-23</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9179,15 +9939,20 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-23</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9239,15 +10004,20 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-23</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9299,15 +10069,20 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-04</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9359,15 +10134,20 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-04</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9419,15 +10199,20 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-04</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9479,15 +10264,20 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-04</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9539,15 +10329,20 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-04</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9599,15 +10394,20 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-04</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9659,15 +10459,20 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-04</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9719,15 +10524,20 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-04</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9779,15 +10589,20 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-04</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9839,15 +10654,20 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-05</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9899,15 +10719,20 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-05</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9959,15 +10784,20 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-05</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10019,15 +10849,20 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-15</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10079,15 +10914,20 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-15</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10139,15 +10979,20 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-15</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10199,15 +11044,20 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-15</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10259,15 +11109,20 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-16</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10319,15 +11174,20 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10379,15 +11239,20 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10439,15 +11304,20 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10494,20 +11364,25 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372982</t>
+          <t xml:space="preserve">311289212</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10554,20 +11429,25 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373089</t>
+          <t xml:space="preserve">311373088</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10619,15 +11499,20 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10679,15 +11564,20 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10739,15 +11629,20 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10794,20 +11689,25 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289245</t>
+          <t xml:space="preserve">311369795</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10859,15 +11759,20 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10919,15 +11824,20 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10979,15 +11889,20 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11039,15 +11954,20 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11099,15 +12019,20 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11159,15 +12084,20 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11219,15 +12149,20 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11279,15 +12214,20 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11339,15 +12279,20 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11399,15 +12344,20 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11459,15 +12409,20 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11519,15 +12474,20 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11574,20 +12534,25 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289296</t>
+          <t xml:space="preserve">311289301</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11639,15 +12604,20 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11699,15 +12669,20 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11759,15 +12734,20 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11819,15 +12799,20 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11879,15 +12864,20 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11939,15 +12929,20 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11999,15 +12994,20 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12059,15 +13059,20 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12119,15 +13124,20 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12179,15 +13189,20 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12239,15 +13254,20 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12299,15 +13319,20 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-19</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12359,15 +13384,20 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-19</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12419,15 +13449,20 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-19</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12479,15 +13514,20 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-19</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12539,15 +13579,20 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-19</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12599,15 +13644,20 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-19</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12659,15 +13709,20 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-19</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12719,15 +13774,20 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-19</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12779,15 +13839,20 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-19</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12839,15 +13904,20 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-19</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12899,15 +13969,20 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-19</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12959,15 +14034,20 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-19</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13019,15 +14099,20 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-22</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13079,15 +14164,20 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-22</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13139,15 +14229,20 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-22</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13199,15 +14294,20 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-22</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13259,15 +14359,20 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-22</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13319,15 +14424,20 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-22</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13379,15 +14489,20 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-22</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13439,15 +14554,20 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-22</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13499,15 +14619,20 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-22</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13559,15 +14684,20 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-22</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13619,15 +14749,20 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-22</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13679,15 +14814,20 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-23</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13739,15 +14879,20 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-23</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13799,15 +14944,20 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-23</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13859,15 +15009,20 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-23</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13919,15 +15074,20 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13979,15 +15139,20 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14039,15 +15204,20 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14099,15 +15269,20 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14159,15 +15334,20 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14219,15 +15399,20 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14279,15 +15464,20 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14339,15 +15529,20 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14399,15 +15594,20 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14459,15 +15659,20 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14519,15 +15724,20 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14579,15 +15789,20 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14639,15 +15854,20 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14699,15 +15919,20 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14759,15 +15984,20 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14819,15 +16049,20 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14874,20 +16109,25 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373101</t>
+          <t xml:space="preserve">311290524</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14939,15 +16179,20 @@
       </c>
       <c r="J249" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14994,20 +16239,25 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290531</t>
+          <t xml:space="preserve">311290529</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15059,15 +16309,20 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15119,15 +16374,20 @@
       </c>
       <c r="J252" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15179,15 +16439,20 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15239,15 +16504,20 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15299,15 +16569,20 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15359,15 +16634,20 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15419,15 +16699,20 @@
       </c>
       <c r="J257" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15479,15 +16764,20 @@
       </c>
       <c r="J258" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15539,15 +16829,20 @@
       </c>
       <c r="J259" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15599,15 +16894,20 @@
       </c>
       <c r="J260" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15659,15 +16959,20 @@
       </c>
       <c r="J261" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15719,15 +17024,20 @@
       </c>
       <c r="J262" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15779,15 +17089,20 @@
       </c>
       <c r="J263" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15839,15 +17154,20 @@
       </c>
       <c r="J264" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15899,15 +17219,20 @@
       </c>
       <c r="J265" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15959,15 +17284,20 @@
       </c>
       <c r="J266" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16019,15 +17349,20 @@
       </c>
       <c r="J267" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16079,15 +17414,20 @@
       </c>
       <c r="J268" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16139,15 +17479,20 @@
       </c>
       <c r="J269" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16199,15 +17544,20 @@
       </c>
       <c r="J270" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16259,15 +17609,20 @@
       </c>
       <c r="J271" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16319,15 +17674,20 @@
       </c>
       <c r="J272" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16379,15 +17739,20 @@
       </c>
       <c r="J273" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16439,15 +17804,20 @@
       </c>
       <c r="J274" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16499,15 +17869,20 @@
       </c>
       <c r="J275" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16559,15 +17934,20 @@
       </c>
       <c r="J276" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16619,15 +17999,20 @@
       </c>
       <c r="J277" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16679,15 +18064,20 @@
       </c>
       <c r="J278" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16739,15 +18129,20 @@
       </c>
       <c r="J279" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16799,15 +18194,20 @@
       </c>
       <c r="J280" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-27</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16859,15 +18259,20 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-28</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16919,15 +18324,20 @@
       </c>
       <c r="J282" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-28</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -16979,15 +18389,20 @@
       </c>
       <c r="J283" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-28</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17039,15 +18454,20 @@
       </c>
       <c r="J284" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-28</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17099,15 +18519,20 @@
       </c>
       <c r="J285" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-28</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17154,20 +18579,25 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290664</t>
+          <t xml:space="preserve">311290663</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-28</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17214,20 +18644,25 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374773</t>
+          <t xml:space="preserve">311290666</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-28</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17279,15 +18714,20 @@
       </c>
       <c r="J288" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-28</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17334,20 +18774,25 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375102</t>
+          <t xml:space="preserve">311375099</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-28</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17399,15 +18844,20 @@
       </c>
       <c r="J290" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-28</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17459,15 +18909,20 @@
       </c>
       <c r="J291" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-28</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17519,15 +18974,20 @@
       </c>
       <c r="J292" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-28</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17579,15 +19039,20 @@
       </c>
       <c r="J293" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-28</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17639,15 +19104,20 @@
       </c>
       <c r="J294" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-28</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17699,15 +19169,20 @@
       </c>
       <c r="J295" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-28</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17759,15 +19234,20 @@
       </c>
       <c r="J296" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-28</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17819,15 +19299,20 @@
       </c>
       <c r="J297" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-28</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17879,15 +19364,20 @@
       </c>
       <c r="J298" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-28</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17934,20 +19424,25 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372662</t>
+          <t xml:space="preserve">311372723</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-29</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -17994,20 +19489,25 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372662</t>
+          <t xml:space="preserve">311372723</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-29</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18059,15 +19559,20 @@
       </c>
       <c r="J301" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-29</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18114,20 +19619,25 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372662</t>
+          <t xml:space="preserve">311372723</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-29</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L302" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18174,20 +19684,25 @@
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372662</t>
+          <t xml:space="preserve">311372723</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-29</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18234,20 +19749,25 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372662</t>
+          <t xml:space="preserve">311372723</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-29</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18299,15 +19819,20 @@
       </c>
       <c r="J305" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-30</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18359,15 +19884,20 @@
       </c>
       <c r="J306" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-30</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18419,15 +19949,20 @@
       </c>
       <c r="J307" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-30</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18479,15 +20014,20 @@
       </c>
       <c r="J308" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-30</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18539,15 +20079,20 @@
       </c>
       <c r="J309" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-30</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18599,15 +20144,20 @@
       </c>
       <c r="J310" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-30</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18659,15 +20209,20 @@
       </c>
       <c r="J311" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-30</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18719,15 +20274,20 @@
       </c>
       <c r="J312" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-04</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18779,15 +20339,20 @@
       </c>
       <c r="J313" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-04</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L313" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18839,15 +20404,20 @@
       </c>
       <c r="J314" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-04</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18899,15 +20469,20 @@
       </c>
       <c r="J315" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-04</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -18959,15 +20534,20 @@
       </c>
       <c r="J316" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-04</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19019,15 +20599,20 @@
       </c>
       <c r="J317" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-04</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19079,15 +20664,20 @@
       </c>
       <c r="J318" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-04</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19139,15 +20729,20 @@
       </c>
       <c r="J319" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-04</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19199,15 +20794,20 @@
       </c>
       <c r="J320" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-04</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19259,15 +20859,20 @@
       </c>
       <c r="J321" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-04</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L321" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19319,15 +20924,20 @@
       </c>
       <c r="J322" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-04</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L322" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19379,15 +20989,20 @@
       </c>
       <c r="J323" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-22</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L323" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19434,20 +21049,25 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379580</t>
+          <t xml:space="preserve">311293850</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-22</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L324" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19499,15 +21119,20 @@
       </c>
       <c r="J325" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-22</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19559,15 +21184,20 @@
       </c>
       <c r="J326" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-22</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L326" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19619,15 +21249,20 @@
       </c>
       <c r="J327" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-22</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L327" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19674,20 +21309,25 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293846</t>
+          <t xml:space="preserve">311293847</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-22</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L328" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19739,15 +21379,20 @@
       </c>
       <c r="J329" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-22</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19794,20 +21439,25 @@
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374142</t>
+          <t xml:space="preserve">311374136</t>
         </is>
       </c>
       <c r="J330" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-22</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L330" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19854,20 +21504,25 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372613</t>
+          <t xml:space="preserve">311293836</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-22</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19919,15 +21574,20 @@
       </c>
       <c r="J332" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-22</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L332" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -19974,20 +21634,25 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293831</t>
+          <t xml:space="preserve">311293836</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-22</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L333" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20039,15 +21704,20 @@
       </c>
       <c r="J334" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-22</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L334" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20099,15 +21769,20 @@
       </c>
       <c r="J335" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-01-22</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L335" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20159,15 +21834,20 @@
       </c>
       <c r="J336" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-02-15</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L336" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20219,15 +21899,20 @@
       </c>
       <c r="J337" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Energisyn</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-04-09</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M337" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20279,15 +21964,20 @@
       </c>
       <c r="J338" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-10-19</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L338" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20339,15 +22029,20 @@
       </c>
       <c r="J339" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ydes Bygningsrådgivning</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-11-17</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L339" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20399,15 +22094,20 @@
       </c>
       <c r="J340" t="inlineStr">
         <is>
+          <t xml:space="preserve">Trykprøvning &amp; Energimærkning Danmark ApS</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-22</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L340" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20459,15 +22159,20 @@
       </c>
       <c r="J341" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-08-12</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L341" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20519,15 +22224,20 @@
       </c>
       <c r="J342" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S - LBF</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-08-11</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L342" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20579,15 +22289,20 @@
       </c>
       <c r="J343" t="inlineStr">
         <is>
+          <t xml:space="preserve">Norconsult A/S</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-04</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L343" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20639,15 +22354,20 @@
       </c>
       <c r="J344" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-09</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20699,15 +22419,20 @@
       </c>
       <c r="J345" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tæthedskompagniet ApS</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-22</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20759,15 +22484,20 @@
       </c>
       <c r="J346" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S - LBF</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-08-27</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L346" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20819,15 +22549,20 @@
       </c>
       <c r="J347" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ydes Bygningsrådgivning</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-06-06</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20879,15 +22614,20 @@
       </c>
       <c r="J348" t="inlineStr">
         <is>
+          <t xml:space="preserve">Trykprøvning &amp; Energimærkning Danmark ApS</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-11-13</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20939,15 +22679,20 @@
       </c>
       <c r="J349" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tæthedskompagniet ApS</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-01-13</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L349" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -20999,15 +22744,20 @@
       </c>
       <c r="J350" t="inlineStr">
         <is>
+          <t xml:space="preserve">Norconsult Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-09-29</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -21059,15 +22809,20 @@
       </c>
       <c r="J351" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tæthedskompagniet ApS</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-11-19</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -21119,21 +22874,26 @@
       </c>
       <c r="J352" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-02-12</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L352" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L352"/>
+  <autoFilter ref="A1:M352"/>
 </worksheet>
 </file>
--- a/public/exports/29189846.xlsx
+++ b/public/exports/29189846.xlsx
@@ -3694,7 +3694,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">200019808</t>
+          <t xml:space="preserve">200019807</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372346</t>
+          <t xml:space="preserve">311372345</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372346</t>
+          <t xml:space="preserve">311372344</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373778</t>
+          <t xml:space="preserve">311373775</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279903</t>
+          <t xml:space="preserve">311279891</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279903</t>
+          <t xml:space="preserve">311279890</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372348</t>
+          <t xml:space="preserve">311282669</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -8114,12 +8114,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311368606</t>
+          <t xml:space="preserve">311284535</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373752</t>
+          <t xml:space="preserve">311373751</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -11689,12 +11689,12 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369795</t>
+          <t xml:space="preserve">311289245</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369795</t>
+          <t xml:space="preserve">311289254</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -11884,12 +11884,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369795</t>
+          <t xml:space="preserve">311289247</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -12534,7 +12534,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289301</t>
+          <t xml:space="preserve">311289296</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -13249,12 +13249,12 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375639</t>
+          <t xml:space="preserve">311375635</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -16304,12 +16304,12 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374076</t>
+          <t xml:space="preserve">311369509</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -18579,12 +18579,12 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290663</t>
+          <t xml:space="preserve">311290661</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
@@ -18839,7 +18839,7 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375108</t>
+          <t xml:space="preserve">311375099</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
@@ -19424,12 +19424,12 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372723</t>
+          <t xml:space="preserve">311372662</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K299" t="inlineStr">
@@ -19489,12 +19489,12 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372723</t>
+          <t xml:space="preserve">311372662</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K300" t="inlineStr">
@@ -19619,12 +19619,12 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372723</t>
+          <t xml:space="preserve">311372662</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K302" t="inlineStr">
@@ -19684,12 +19684,12 @@
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372723</t>
+          <t xml:space="preserve">311372662</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K303" t="inlineStr">
@@ -19749,12 +19749,12 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372723</t>
+          <t xml:space="preserve">311372662</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K304" t="inlineStr">
@@ -20399,12 +20399,12 @@
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373742</t>
+          <t xml:space="preserve">311291095</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K314" t="inlineStr">
@@ -21309,7 +21309,7 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293847</t>
+          <t xml:space="preserve">311293846</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
@@ -21634,7 +21634,7 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293836</t>
+          <t xml:space="preserve">311293831</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
@@ -21699,7 +21699,7 @@
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293836</t>
+          <t xml:space="preserve">311293833</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
